--- a/ARISTA_Ex3A_tables.xlsx
+++ b/ARISTA_Ex3A_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/tarista_my_yearupunited_org/Documents/Documents/DATA_Labs/W2_Workshop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="11_F25DC773A252ABDACC104807991E5C8C5ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86581438-921A-4A22-B80B-D8BB1390144E}"/>
+  <xr:revisionPtr revIDLastSave="193" documentId="11_F25DC773A252ABDACC104807991E5C8C5ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FDFAE29-2CB3-414E-B948-14D72A69C9F6}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lana's dog-walking" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
   <si>
     <t>Clients</t>
   </si>
@@ -102,6 +102,90 @@
   </si>
   <si>
     <t>payment_method</t>
+  </si>
+  <si>
+    <t>sarah</t>
+  </si>
+  <si>
+    <t>michael</t>
+  </si>
+  <si>
+    <t>emily</t>
+  </si>
+  <si>
+    <t>davis</t>
+  </si>
+  <si>
+    <t>brown</t>
+  </si>
+  <si>
+    <t>johnson</t>
+  </si>
+  <si>
+    <t>555-123-4567</t>
+  </si>
+  <si>
+    <t>555-222-1111</t>
+  </si>
+  <si>
+    <t>555-333-4444</t>
+  </si>
+  <si>
+    <t>78 oak rd</t>
+  </si>
+  <si>
+    <t>45 lake ave</t>
+  </si>
+  <si>
+    <t>123 main st</t>
+  </si>
+  <si>
+    <t>rocky</t>
+  </si>
+  <si>
+    <t>luna</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>buddy</t>
+  </si>
+  <si>
+    <t>golden retriver</t>
+  </si>
+  <si>
+    <t>german shepherd</t>
+  </si>
+  <si>
+    <t>poodle</t>
+  </si>
+  <si>
+    <t>bulldog</t>
+  </si>
+  <si>
+    <t>very friendly</t>
+  </si>
+  <si>
+    <t>proctective</t>
+  </si>
+  <si>
+    <t>shy around strangers</t>
+  </si>
+  <si>
+    <t>loves short walks</t>
+  </si>
+  <si>
+    <t>scheduled</t>
+  </si>
+  <si>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>card</t>
+  </si>
+  <si>
+    <t>cash</t>
   </si>
 </sst>
 </file>
@@ -149,10 +233,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -466,7 +552,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56C95DB-0247-4580-8ED8-20FDA19703B3}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" customWidth="1"/>
@@ -493,6 +579,57 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -500,7 +637,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE2295B-2E65-4FB9-83DC-328747B301BE}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.44140625" customWidth="1"/>
@@ -530,6 +667,86 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -537,7 +754,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE04C50F-0239-4490-B977-3285F806EFE6}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.5546875" customWidth="1"/>
@@ -563,6 +780,57 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3">
+        <v>46128</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3">
+        <v>46128</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D3">
+        <v>45</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>46129</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.375</v>
+      </c>
+      <c r="D4">
+        <v>60</v>
+      </c>
+      <c r="E4" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -570,7 +838,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{146D7775-8A7B-49AD-8C6B-B87B5B49D6E2}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -589,6 +857,50 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -596,7 +908,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E6E4A44-23E0-4278-B012-DAF2E4D82114}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
@@ -627,6 +939,63 @@
         <v>23</v>
       </c>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>40</v>
+      </c>
+      <c r="E2" s="3">
+        <v>46128</v>
+      </c>
+      <c r="F2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>25</v>
+      </c>
+      <c r="E4" s="3">
+        <v>46129</v>
+      </c>
+      <c r="F4" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ARISTA_Ex3A_tables.xlsx
+++ b/ARISTA_Ex3A_tables.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="193" documentId="11_F25DC773A252ABDACC104807991E5C8C5ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FDFAE29-2CB3-414E-B948-14D72A69C9F6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lana's dog-walking" sheetId="1" r:id="rId1"/>
